--- a/config.xlsx
+++ b/config.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="61">
   <si>
     <t>提示词</t>
   </si>
@@ -70,6 +70,9 @@
     <t>批量功能</t>
   </si>
   <si>
+    <t>链式调用的函数</t>
+  </si>
+  <si>
     <t>prompt</t>
   </si>
   <si>
@@ -109,7 +112,13 @@
     <t>batchFun</t>
   </si>
   <si>
-    <t>referenceImages/谷歌地图2</t>
+    <t>nextPromptFun</t>
+  </si>
+  <si>
+    <t>生成一张1:1的方图，适当调整构图使应用的图标战图比例变大在显眼位置</t>
+  </si>
+  <si>
+    <t>referenceImages/line方</t>
   </si>
   <si>
     <t>1:1</t>
@@ -118,61 +127,91 @@
     <t>1k</t>
   </si>
   <si>
-    <t>D:\mog素材\待用素材库\谷歌地图\方</t>
-  </si>
-  <si>
-    <t>谷歌地图</t>
+    <t>D:\mog素材\待用素材库\line方2</t>
+  </si>
+  <si>
+    <t>Gmail</t>
   </si>
   <si>
     <t>jp</t>
   </si>
   <si>
+    <t>batch</t>
+  </si>
+  <si>
+    <t>要使用参考图的按钮类型的图标、简约风格，发挥创意</t>
+  </si>
+  <si>
+    <t>referenceImages/Gmail</t>
+  </si>
+  <si>
+    <t>16:9</t>
+  </si>
+  <si>
+    <t>D:\mog素材\待用素材库\谷歌邮箱</t>
+  </si>
+  <si>
+    <t>getAppDefaultPrompt</t>
+  </si>
+  <si>
+    <t>referenceImages/line</t>
+  </si>
+  <si>
+    <t>4:5</t>
+  </si>
+  <si>
+    <t>D:\mog素材\待用素材库\line竖2</t>
+  </si>
+  <si>
+    <t>line</t>
+  </si>
+  <si>
     <t>getCutLogoPrompt</t>
   </si>
   <si>
-    <t>batch</t>
-  </si>
-  <si>
-    <t>referenceImages/2</t>
-  </si>
-  <si>
-    <t>16:9</t>
-  </si>
-  <si>
-    <t>D:\mog素材\待用素材库\谷歌邮箱</t>
-  </si>
-  <si>
-    <t>Gmail</t>
+    <t>getCentralPositionPrompt</t>
+  </si>
+  <si>
+    <t>发挥创意调整构图结构、不要科幻风格</t>
+  </si>
+  <si>
+    <t>referenceImages/YouTube</t>
+  </si>
+  <si>
+    <t>D:\mog素材\待用素材库\YouTube</t>
+  </si>
+  <si>
+    <t>YouTube</t>
   </si>
   <si>
     <t>us</t>
   </si>
   <si>
-    <t>getAppAdsDesignerPrompt,getAppDefaultPrompt</t>
+    <t>combination2</t>
+  </si>
+  <si>
+    <t>D:\mog素材\待用素材库\line</t>
+  </si>
+  <si>
+    <t>getAppAdsDesignerPrompt</t>
+  </si>
+  <si>
+    <t>D:\mog素材\待用素材库\YouTube方\1768535732148-1200x628</t>
+  </si>
+  <si>
+    <t>D:\mog素材\待用素材库\YouTube方\1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                  </t>
+  </si>
+  <si>
+    <t>2k</t>
   </si>
   <si>
     <t>combination</t>
   </si>
   <si>
-    <t>referenceImages/4</t>
-  </si>
-  <si>
-    <t>getCutImagePrompt</t>
-  </si>
-  <si>
-    <t>2k</t>
-  </si>
-  <si>
-    <t>4:5</t>
-  </si>
-  <si>
-    <t>D:\mog素材\待用素材库\谷歌地图</t>
-  </si>
-  <si>
-    <t>Gmail map</t>
-  </si>
-  <si>
-    <t>getAppDefaultPrompt3</t>
+    <t>combination3</t>
   </si>
 </sst>
 </file>
@@ -800,7 +839,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -820,6 +859,9 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1206,25 +1248,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="40.375" customWidth="1"/>
+    <col min="1" max="1" width="47.625" customWidth="1"/>
     <col min="2" max="2" width="25.5" customWidth="1"/>
     <col min="3" max="3" width="16.875" customWidth="1"/>
-    <col min="4" max="4" width="15.125" customWidth="1"/>
-    <col min="5" max="5" width="16.25" customWidth="1"/>
-    <col min="6" max="6" width="25.5" style="6" customWidth="1"/>
-    <col min="7" max="7" width="35.875" customWidth="1"/>
+    <col min="4" max="4" width="6.75" customWidth="1"/>
+    <col min="5" max="5" width="6.25" customWidth="1"/>
+    <col min="6" max="6" width="6.25" style="6" customWidth="1"/>
+    <col min="7" max="7" width="4.125" customWidth="1"/>
     <col min="8" max="8" width="37.875" customWidth="1"/>
-    <col min="9" max="9" width="9.5" customWidth="1"/>
+    <col min="9" max="9" width="6.5" customWidth="1"/>
     <col min="10" max="10" width="17.25" customWidth="1"/>
     <col min="11" max="11" width="9.125" customWidth="1"/>
     <col min="12" max="12" width="22.75" customWidth="1"/>
-    <col min="13" max="13" width="12.25" customWidth="1"/>
+    <col min="13" max="13" width="13.875" customWidth="1"/>
+    <col min="14" max="14" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="8" customFormat="1" ht="15" customHeight="1" spans="1:13">
+    <row r="1" s="8" customFormat="1" ht="15" customHeight="1" spans="1:14">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1264,169 +1307,278 @@
       <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="8" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" s="8" customFormat="1" spans="1:13">
+    <row r="2" s="8" customFormat="1" spans="1:14">
       <c r="A2" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="3" ht="18" spans="1:13">
-      <c r="A3" s="7"/>
+    <row r="3" ht="18" spans="1:14">
+      <c r="A3" s="7" t="s">
+        <v>28</v>
+      </c>
       <c r="B3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3"/>
-      <c r="E3"/>
+        <v>29</v>
+      </c>
+      <c r="C3"/>
       <c r="F3" s="6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K3" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="11"/>
+      <c r="M3" t="s">
+        <v>35</v>
+      </c>
+      <c r="N3" s="11"/>
+    </row>
+    <row r="4" customFormat="1" ht="36" spans="1:14">
+      <c r="A4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4">
+        <v>1.1</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" t="s">
         <v>31</v>
       </c>
-      <c r="L3" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" customFormat="1" ht="54" spans="1:13">
-      <c r="A4" s="7"/>
-      <c r="B4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4">
-        <v>1.8</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" t="s">
-        <v>28</v>
-      </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="K4" t="s">
-        <v>38</v>
-      </c>
-      <c r="L4" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="M4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="12" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="5" customFormat="1" ht="18" spans="1:13">
+    <row r="5" customFormat="1" ht="54" spans="1:14">
       <c r="A5" s="7"/>
       <c r="B5" t="s">
         <v>41</v>
       </c>
-      <c r="C5"/>
+      <c r="C5">
+        <v>0.5</v>
+      </c>
       <c r="F5" s="6" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H5" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J5" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="K5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="M5" t="s">
+        <v>35</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="36" spans="1:14">
+      <c r="A6" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6">
+        <v>1.8</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="K6" t="s">
+        <v>51</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="M6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" ht="36" spans="1:14">
+      <c r="A7" s="7"/>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7">
+        <v>1.1</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" t="s">
+        <v>53</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="K7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" ht="36" spans="1:14">
+      <c r="A8" s="7"/>
+      <c r="B8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8">
+        <v>0.5</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="K5" t="s">
-        <v>38</v>
-      </c>
-      <c r="L5" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="M5" t="s">
-        <v>33</v>
+      <c r="G8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" t="s">
+        <v>51</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="M8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="J16" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3 F4 F5 F1:F2 F6:F1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6 F7 F8 F1:F5 F9:F1048576">
       <formula1>Sheet3!$B$1:$B$10</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3 M4 M5 M1:M2 M6:M1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G6 G7 G8 G1:G5 G9:G1048576">
+      <formula1>Sheet3!$A$1:$A$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M6 M7 M8 M1:M5 M9:M1048576">
       <formula1>Sheet3!$C:$C</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4 G5 G1:G3 G6:G1048576">
-      <formula1>Sheet3!$A$1:$A$10</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="G2:G3 A2 A1:B1 D1:I1 C2:E2 I2" numberStoredAsText="1"/>
+    <ignoredError sqref="I2 C2:E2 D1:I1 A1:B1 A2 G2:G3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1434,8 +1586,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="2" outlineLevelCol="2"/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="12.625" style="6"/>
     <col min="2" max="2" width="9" style="6"/>
@@ -1444,29 +1596,37 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="6" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="B3" s="6" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="C4" s="7" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1481,32 +1641,16 @@
   <dimension ref="A1:L1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="72" spans="1:12">
+    <row r="1" s="1" customFormat="1" ht="18" spans="1:12">
       <c r="A1" s="2"/>
-      <c r="B1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I1" s="1">
-        <v>5</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>47</v>
-      </c>
+      <c r="B1" s="1"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="5"/>
     </row>
   </sheetData>
   <dataValidations count="3">

--- a/config.xlsx
+++ b/config.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="60">
   <si>
     <t>提示词</t>
   </si>
@@ -118,7 +118,7 @@
     <t>生成一张1:1的方图，适当调整构图使应用的图标战图比例变大在显眼位置</t>
   </si>
   <si>
-    <t>referenceImages/line方</t>
+    <t>referenceImages/line</t>
   </si>
   <si>
     <t>1:1</t>
@@ -152,9 +152,6 @@
   </si>
   <si>
     <t>getAppDefaultPrompt</t>
-  </si>
-  <si>
-    <t>referenceImages/line</t>
   </si>
   <si>
     <t>4:5</t>
@@ -839,7 +836,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -859,9 +856,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1362,7 +1356,6 @@
       <c r="B3" t="s">
         <v>29</v>
       </c>
-      <c r="C3"/>
       <c r="F3" s="6" t="s">
         <v>30</v>
       </c>
@@ -1417,52 +1410,52 @@
       <c r="K4" t="s">
         <v>34</v>
       </c>
-      <c r="L4" s="12" t="s">
+      <c r="L4" s="11" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="5" customFormat="1" ht="54" spans="1:14">
       <c r="A5" s="7"/>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C5">
         <v>0.5</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G5" t="s">
         <v>31</v>
       </c>
       <c r="H5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K5" t="s">
         <v>34</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M5" t="s">
         <v>35</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" customFormat="1" ht="36" spans="1:14">
       <c r="A6" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s">
         <v>47</v>
-      </c>
-      <c r="B6" t="s">
-        <v>48</v>
       </c>
       <c r="C6">
         <v>1.8</v>
@@ -1474,28 +1467,28 @@
         <v>31</v>
       </c>
       <c r="H6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K6" t="s">
         <v>50</v>
-      </c>
-      <c r="K6" t="s">
-        <v>51</v>
       </c>
       <c r="L6" s="11" t="s">
         <v>40</v>
       </c>
       <c r="M6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="36" spans="1:14">
       <c r="A7" s="7"/>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C7">
         <v>1.1</v>
@@ -1507,28 +1500,28 @@
         <v>31</v>
       </c>
       <c r="H7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K7" t="s">
         <v>34</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" customFormat="1" ht="36" spans="1:14">
       <c r="A8" s="7"/>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C8">
         <v>0.5</v>
@@ -1540,19 +1533,19 @@
         <v>31</v>
       </c>
       <c r="H8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K8" t="s">
         <v>50</v>
       </c>
-      <c r="K8" t="s">
-        <v>51</v>
-      </c>
       <c r="L8" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M8" t="s">
         <v>35</v>
@@ -1560,25 +1553,25 @@
     </row>
     <row r="16" spans="1:14">
       <c r="J16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6 F7 F8 F1:F5 F9:F1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576">
       <formula1>Sheet3!$B$1:$B$10</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G6 G7 G8 G1:G5 G9:G1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G$1:G$1048576">
       <formula1>Sheet3!$A$1:$A$10</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M6 M7 M8 M1:M5 M9:M1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M$1:M$1048576">
       <formula1>Sheet3!$C:$C</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="I2 C2:E2 D1:I1 A1:B1 A2 G2:G3" numberStoredAsText="1"/>
+    <ignoredError sqref="G2:G3 A2 A1:B1 D1:I1 C2:E2 I2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1607,13 +1600,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>58</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1621,12 +1614,12 @@
         <v>38</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="C4" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/config.xlsx
+++ b/config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="10725"/>
+    <workbookView windowHeight="10725"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="67">
   <si>
     <t>提示词</t>
   </si>
@@ -115,94 +115,115 @@
     <t>nextPromptFun</t>
   </si>
   <si>
-    <t>生成一张1:1的方图，适当调整构图使应用的图标战图比例变大在显眼位置</t>
+    <t>referenceImages/1-19/寿司方竖</t>
+  </si>
+  <si>
+    <t>1K</t>
+  </si>
+  <si>
+    <t>D:\mog素材\待用素材库\寿司</t>
+  </si>
+  <si>
+    <t>はま寿司</t>
+  </si>
+  <si>
+    <t>jp</t>
+  </si>
+  <si>
+    <t>cut</t>
+  </si>
+  <si>
+    <t>referenceImages/1-19/谷歌地图转us</t>
+  </si>
+  <si>
+    <t>16:9</t>
+  </si>
+  <si>
+    <t>D:\mog素材\待用素材库\谷歌地图转us</t>
+  </si>
+  <si>
+    <t>谷歌地图</t>
+  </si>
+  <si>
+    <t>us</t>
+  </si>
+  <si>
+    <t>getTextTranslatePrompt</t>
+  </si>
+  <si>
+    <t>batch</t>
+  </si>
+  <si>
+    <t>自然风景背景</t>
+  </si>
+  <si>
+    <t>D:\batchGenerateImage\referenceImages\1-20\naver\自然风景</t>
+  </si>
+  <si>
+    <t>D:\mog素材\待用素材库\naver自然背景</t>
+  </si>
+  <si>
+    <t>naver</t>
+  </si>
+  <si>
+    <t>kr</t>
+  </si>
+  <si>
+    <t>getAppAdsDesignerPrompt</t>
+  </si>
+  <si>
+    <t>combination2</t>
   </si>
   <si>
     <t>referenceImages/line</t>
   </si>
   <si>
+    <t>4:5</t>
+  </si>
+  <si>
+    <t>D:\mog素材\待用素材库\line竖2</t>
+  </si>
+  <si>
+    <t>line</t>
+  </si>
+  <si>
+    <t>getCutLogoPrompt</t>
+  </si>
+  <si>
+    <t>getCentralPositionPrompt</t>
+  </si>
+  <si>
+    <t>发挥创意调整构图结构、不要科幻风格</t>
+  </si>
+  <si>
+    <t>referenceImages/YouTube</t>
+  </si>
+  <si>
+    <t>D:\mog素材\待用素材库\YouTube</t>
+  </si>
+  <si>
+    <t>YouTube</t>
+  </si>
+  <si>
+    <t>getAppDefaultPrompt</t>
+  </si>
+  <si>
+    <t>D:\mog素材\待用素材库\line</t>
+  </si>
+  <si>
+    <t>D:\mog素材\待用素材库\YouTube方\1768535732148-1200x628</t>
+  </si>
+  <si>
     <t>1:1</t>
   </si>
   <si>
-    <t>1k</t>
-  </si>
-  <si>
-    <t>D:\mog素材\待用素材库\line方2</t>
-  </si>
-  <si>
-    <t>Gmail</t>
-  </si>
-  <si>
-    <t>jp</t>
-  </si>
-  <si>
-    <t>batch</t>
-  </si>
-  <si>
-    <t>要使用参考图的按钮类型的图标、简约风格，发挥创意</t>
-  </si>
-  <si>
-    <t>referenceImages/Gmail</t>
-  </si>
-  <si>
-    <t>16:9</t>
-  </si>
-  <si>
-    <t>D:\mog素材\待用素材库\谷歌邮箱</t>
-  </si>
-  <si>
-    <t>getAppDefaultPrompt</t>
-  </si>
-  <si>
-    <t>4:5</t>
-  </si>
-  <si>
-    <t>D:\mog素材\待用素材库\line竖2</t>
-  </si>
-  <si>
-    <t>line</t>
-  </si>
-  <si>
-    <t>getCutLogoPrompt</t>
-  </si>
-  <si>
-    <t>getCentralPositionPrompt</t>
-  </si>
-  <si>
-    <t>发挥创意调整构图结构、不要科幻风格</t>
-  </si>
-  <si>
-    <t>referenceImages/YouTube</t>
-  </si>
-  <si>
-    <t>D:\mog素材\待用素材库\YouTube</t>
-  </si>
-  <si>
-    <t>YouTube</t>
-  </si>
-  <si>
-    <t>us</t>
-  </si>
-  <si>
-    <t>combination2</t>
-  </si>
-  <si>
-    <t>D:\mog素材\待用素材库\line</t>
-  </si>
-  <si>
-    <t>getAppAdsDesignerPrompt</t>
-  </si>
-  <si>
-    <t>D:\mog素材\待用素材库\YouTube方\1768535732148-1200x628</t>
-  </si>
-  <si>
     <t>D:\mog素材\待用素材库\YouTube方\1</t>
   </si>
   <si>
     <t xml:space="preserve">                  </t>
   </si>
   <si>
-    <t>2k</t>
+    <t>2K</t>
   </si>
   <si>
     <t>combination</t>
@@ -836,7 +857,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -856,6 +877,10 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1242,16 +1267,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="47.625" customWidth="1"/>
-    <col min="2" max="2" width="25.5" customWidth="1"/>
-    <col min="3" max="3" width="16.875" customWidth="1"/>
+    <col min="1" max="1" width="73.125" customWidth="1"/>
+    <col min="2" max="2" width="32.25" customWidth="1"/>
+    <col min="3" max="3" width="8.5" customWidth="1"/>
     <col min="4" max="4" width="6.75" customWidth="1"/>
     <col min="5" max="5" width="6.25" customWidth="1"/>
     <col min="6" max="6" width="6.25" style="6" customWidth="1"/>
-    <col min="7" max="7" width="4.125" customWidth="1"/>
+    <col min="7" max="7" width="7.75" customWidth="1"/>
     <col min="8" max="8" width="37.875" customWidth="1"/>
     <col min="9" max="9" width="6.5" customWidth="1"/>
     <col min="10" max="10" width="17.25" customWidth="1"/>
@@ -1350,228 +1375,260 @@
       </c>
     </row>
     <row r="3" ht="18" spans="1:14">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="7"/>
+      <c r="B3" t="s">
         <v>28</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3"/>
+      <c r="G3" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="H3" t="s">
         <v>30</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H3" t="s">
+      <c r="K3" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3" s="8" t="s">
+      <c r="L3" s="12"/>
+      <c r="M3" t="s">
         <v>33</v>
       </c>
-      <c r="K3" t="s">
-        <v>34</v>
-      </c>
-      <c r="L3" s="11"/>
-      <c r="M3" t="s">
-        <v>35</v>
-      </c>
-      <c r="N3" s="11"/>
+      <c r="N3" s="13"/>
     </row>
     <row r="4" customFormat="1" ht="36" spans="1:14">
-      <c r="A4" s="7" t="s">
-        <v>36</v>
-      </c>
+      <c r="A4" s="7"/>
       <c r="B4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4">
-        <v>1.1</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="C4"/>
       <c r="D4"/>
       <c r="E4"/>
       <c r="F4" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" t="s">
-        <v>31</v>
+        <v>35</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>29</v>
       </c>
       <c r="H4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="K4" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" s="11" t="s">
+      <c r="J4" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L4" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4" t="s">
         <v>40</v>
       </c>
+      <c r="N4" s="13"/>
     </row>
-    <row r="5" customFormat="1" ht="54" spans="1:14">
-      <c r="A5" s="7"/>
+    <row r="5" customFormat="1" ht="36" customHeight="1" spans="1:14">
+      <c r="A5" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="B5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5">
+        <v>1.1</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C5">
+      <c r="H5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5">
+        <v>15</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="K5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="M5" t="s">
+        <v>47</v>
+      </c>
+      <c r="N5" s="13"/>
+    </row>
+    <row r="6" customFormat="1" ht="54" spans="1:14">
+      <c r="A6" s="7"/>
+      <c r="B6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6">
         <v>0.5</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="K5" t="s">
-        <v>34</v>
-      </c>
-      <c r="L5" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="M5" t="s">
-        <v>35</v>
-      </c>
-      <c r="N5" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" customFormat="1" ht="36" spans="1:14">
-      <c r="A6" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6">
-        <v>1.8</v>
-      </c>
       <c r="F6" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" t="s">
-        <v>31</v>
+        <v>49</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>29</v>
       </c>
       <c r="H6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K6" t="s">
-        <v>50</v>
-      </c>
-      <c r="L6" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="M6" t="s">
         <v>40</v>
       </c>
-      <c r="M6" t="s">
-        <v>51</v>
+      <c r="N6" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="36" spans="1:14">
-      <c r="A7" s="7"/>
+      <c r="A7" s="7" t="s">
+        <v>54</v>
+      </c>
       <c r="B7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7">
+        <v>1.8</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C7">
-        <v>1.1</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" t="s">
-        <v>31</v>
-      </c>
       <c r="H7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="K7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L7" s="11" t="s">
-        <v>53</v>
+        <v>38</v>
+      </c>
+      <c r="L7" s="13" t="s">
+        <v>58</v>
       </c>
       <c r="M7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" customFormat="1" ht="36" spans="1:14">
       <c r="A8" s="7"/>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" t="s">
-        <v>31</v>
+        <v>35</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>29</v>
       </c>
       <c r="H8" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K8" t="s">
-        <v>50</v>
-      </c>
-      <c r="L8" s="11" t="s">
-        <v>45</v>
+        <v>32</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>46</v>
       </c>
       <c r="M8" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
-      <c r="J16" t="s">
-        <v>56</v>
+    <row r="9" customFormat="1" ht="36" spans="1:14">
+      <c r="A9" s="7"/>
+      <c r="B9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9">
+        <v>0.5</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" t="s">
+        <v>62</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="K9" t="s">
+        <v>38</v>
+      </c>
+      <c r="L9" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="M9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="10:10">
+      <c r="J17" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3 G4 G5 G1:G2 G6:G9 G10:G1048576">
+      <formula1>Sheet3!$A$1:$A$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4 F5 F1:F3 F6:F1048576">
       <formula1>Sheet3!$B$1:$B$10</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G$1:G$1048576">
-      <formula1>Sheet3!$A$1:$A$10</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M$1:M$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M4 M5 M1:M3 M6:M1048576">
       <formula1>Sheet3!$C:$C</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="G2:G3 A2 A1:B1 D1:I1 C2:E2 I2" numberStoredAsText="1"/>
+    <ignoredError sqref="C2:E2 D1:I1 A1:B1 A2 G2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1579,8 +1636,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3" outlineLevelCol="2"/>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="12.625" style="6"/>
     <col min="2" max="2" width="9" style="6"/>
@@ -1589,37 +1646,42 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="6" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="B3" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="C4" s="7" t="s">
-        <v>59</v>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="C5" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/config.xlsx
+++ b/config.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="73">
   <si>
     <t>提示词</t>
   </si>
@@ -173,6 +173,24 @@
   </si>
   <si>
     <t>combination2</t>
+  </si>
+  <si>
+    <t>logo+文字+图形组成画面，背景需要纯色就好可以有一些略微条纹变化</t>
+  </si>
+  <si>
+    <t>D:\batchGenerateImage\referenceImages\1-20\naver\纯logo排版</t>
+  </si>
+  <si>
+    <t>D:\mog素材\待用素材库\naver纯logo排版</t>
+  </si>
+  <si>
+    <t>地铁背景（线路图/实拍场景/地图）</t>
+  </si>
+  <si>
+    <t>D:\batchGenerateImage\referenceImages\1-20\naver\地铁线路背景</t>
+  </si>
+  <si>
+    <t>D:\mog素材\待用素材库\naver地铁线路背景</t>
   </si>
   <si>
     <t>referenceImages/line</t>
@@ -1267,7 +1285,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="73.125" customWidth="1"/>
@@ -1471,16 +1489,18 @@
       </c>
       <c r="N5" s="13"/>
     </row>
-    <row r="6" customFormat="1" ht="54" spans="1:14">
-      <c r="A6" s="7"/>
+    <row r="6" customFormat="1" ht="36" customHeight="1" spans="1:14">
+      <c r="A6" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>29</v>
@@ -1489,33 +1509,31 @@
         <v>50</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J6" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="K6" t="s">
+        <v>45</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="M6" t="s">
+        <v>47</v>
+      </c>
+      <c r="N6" s="13"/>
+    </row>
+    <row r="7" customFormat="1" ht="36" customHeight="1" spans="1:14">
+      <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="K6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L6" s="13" t="s">
+      <c r="B7" t="s">
         <v>52</v>
       </c>
-      <c r="M6" t="s">
-        <v>40</v>
-      </c>
-      <c r="N6" s="13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" customFormat="1" ht="36" spans="1:14">
-      <c r="A7" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" t="s">
-        <v>55</v>
-      </c>
       <c r="C7">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>35</v>
@@ -1524,67 +1542,73 @@
         <v>29</v>
       </c>
       <c r="H7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="K7" t="s">
-        <v>38</v>
-      </c>
-      <c r="L7" s="13" t="s">
-        <v>58</v>
+        <v>45</v>
+      </c>
+      <c r="L7" s="12" t="s">
+        <v>46</v>
       </c>
       <c r="M7" t="s">
         <v>47</v>
       </c>
+      <c r="N7" s="13"/>
     </row>
-    <row r="8" customFormat="1" ht="36" spans="1:14">
+    <row r="8" customFormat="1" ht="54" spans="1:14">
       <c r="A8" s="7"/>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C8">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="G8" s="11" t="s">
         <v>29</v>
       </c>
       <c r="H8" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="K8" t="s">
         <v>32</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="M8" t="s">
-        <v>47</v>
+        <v>40</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="9" customFormat="1" ht="36" spans="1:14">
-      <c r="A9" s="7"/>
+      <c r="A9" s="7" t="s">
+        <v>60</v>
+      </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C9">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="G9" s="11" t="s">
         <v>29</v>
@@ -1596,32 +1620,98 @@
         <v>0</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="K9" t="s">
         <v>38</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="M9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" ht="36" spans="1:14">
+      <c r="A10" s="7"/>
+      <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10">
+        <v>1.1</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" t="s">
+        <v>65</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="K10" t="s">
+        <v>32</v>
+      </c>
+      <c r="L10" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="M10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" ht="36" spans="1:14">
+      <c r="A11" s="7"/>
+      <c r="B11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11">
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" t="s">
+        <v>68</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="K11" t="s">
+        <v>38</v>
+      </c>
+      <c r="L11" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="M11" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="10:10">
-      <c r="J17" t="s">
-        <v>63</v>
+    <row r="19" spans="10:10">
+      <c r="J19" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3 G4 G5 G1:G2 G6:G9 G10:G1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3 G4 G5 G6 G7 G1:G2 G8:G11 G12:G1048576">
       <formula1>Sheet3!$A$1:$A$10</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4 F5 F1:F3 F6:F1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4 F5 F6 F7 F1:F3 F8:F1048576">
       <formula1>Sheet3!$B$1:$B$10</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M4 M5 M1:M3 M6:M1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M4 M5 M6 M7 M1:M3 M8:M1048576">
       <formula1>Sheet3!$C:$C</formula1>
     </dataValidation>
   </dataValidations>
@@ -1649,7 +1739,7 @@
         <v>29</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>40</v>
@@ -1657,13 +1747,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="6" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1676,7 +1766,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="C4" s="7" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:3">

--- a/config.xlsx
+++ b/config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="10725"/>
+    <workbookView windowWidth="31290" windowHeight="10725"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="86">
   <si>
     <t>提示词</t>
   </si>
@@ -115,97 +115,176 @@
     <t>nextPromptFun</t>
   </si>
   <si>
-    <t>referenceImages/1-19/寿司方竖</t>
+    <t>D:\batchGenerateImage\referenceImages\1-20\gmail方竖</t>
   </si>
   <si>
     <t>1K</t>
   </si>
   <si>
-    <t>D:\mog素材\待用素材库\寿司</t>
+    <t>D:\mog素材\待用素材库\gmail方竖</t>
+  </si>
+  <si>
+    <t>gamil</t>
+  </si>
+  <si>
+    <t>us</t>
+  </si>
+  <si>
+    <t>cut</t>
+  </si>
+  <si>
+    <t>D:\mog素材\xjt\gmail\0120-us</t>
+  </si>
+  <si>
+    <t>D:\mog素材\xjt\gmail\0120-jp</t>
+  </si>
+  <si>
+    <t>jp</t>
+  </si>
+  <si>
+    <t>translate</t>
+  </si>
+  <si>
+    <t>D:\batchGenerateImage\referenceImages\1-20\naver方竖\地铁线路背景</t>
+  </si>
+  <si>
+    <t>D:\mog素材\待用素材库\naver方竖</t>
+  </si>
+  <si>
+    <t>naver</t>
+  </si>
+  <si>
+    <t>kr</t>
+  </si>
+  <si>
+    <t>D:\batchGenerateImage\referenceImages\1-20\naver方竖\自然风景</t>
+  </si>
+  <si>
+    <r>
+      <t>应用的图标跟参考图要保持一抹一样。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>文案参考使用： 100円祭り開催中!或者</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>厳選ネタが、ぜんぶ110円</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 或者:売り切れ御免！はま寿司の100円祭り</t>
+    </r>
+  </si>
+  <si>
+    <t>referenceImages/1-21/寿司</t>
+  </si>
+  <si>
+    <t>16:9</t>
+  </si>
+  <si>
+    <t>D:\mog素材\待用素材库\1-21寿司</t>
   </si>
   <si>
     <t>はま寿司</t>
   </si>
   <si>
-    <t>jp</t>
-  </si>
-  <si>
-    <t>cut</t>
-  </si>
-  <si>
-    <t>referenceImages/1-19/谷歌地图转us</t>
-  </si>
-  <si>
-    <t>16:9</t>
-  </si>
-  <si>
-    <t>D:\mog素材\待用素材库\谷歌地图转us</t>
-  </si>
-  <si>
-    <t>谷歌地图</t>
-  </si>
-  <si>
-    <t>us</t>
-  </si>
-  <si>
-    <t>getTextTranslatePrompt</t>
+    <t>getAppAdsDesignerPrompt</t>
+  </si>
+  <si>
+    <t>combination2</t>
+  </si>
+  <si>
+    <t>应用的图标跟参考图要保持一抹一样。根据参考图的结构构图更换不同人物以及背景</t>
+  </si>
+  <si>
+    <t>referenceImages/1-21/xjt寿司</t>
+  </si>
+  <si>
+    <t>D:\mog素材\待用素材库\1-21xjt寿司</t>
+  </si>
+  <si>
+    <t>商务风格，背景简约</t>
+  </si>
+  <si>
+    <t>D:\batchGenerateImage\referenceImages\1-21\line商务感</t>
+  </si>
+  <si>
+    <t>D:\mog素材\待用素材库\1-21 line商务感</t>
+  </si>
+  <si>
+    <t>line</t>
+  </si>
+  <si>
+    <t>白色底</t>
+  </si>
+  <si>
+    <t>D:\batchGenerateImage\referenceImages\1-20\gmail2</t>
+  </si>
+  <si>
+    <t>D:\mog素材\待用素材库\谷歌邮箱</t>
+  </si>
+  <si>
+    <t>谷歌邮箱</t>
+  </si>
+  <si>
+    <t>logo+文字+图形组成画面，背景需要纯色就好可以有一些略微条纹变化</t>
+  </si>
+  <si>
+    <t>D:\batchGenerateImage\referenceImages\1-20\naver\纯logo排版</t>
+  </si>
+  <si>
+    <t>D:\mog素材\待用素材库\naver纯logo排版</t>
+  </si>
+  <si>
+    <t>地铁背景（线路图/实拍场景/地图）</t>
+  </si>
+  <si>
+    <t>D:\batchGenerateImage\referenceImages\1-20\naver\地铁线路背景</t>
+  </si>
+  <si>
+    <t>D:\mog素材\待用素材库\naver地铁线路背景</t>
+  </si>
+  <si>
+    <t>referenceImages/line</t>
+  </si>
+  <si>
+    <t>4:5</t>
+  </si>
+  <si>
+    <t>D:\mog素材\待用素材库\line竖2</t>
+  </si>
+  <si>
+    <t>getCutLogoPrompt</t>
   </si>
   <si>
     <t>batch</t>
-  </si>
-  <si>
-    <t>自然风景背景</t>
-  </si>
-  <si>
-    <t>D:\batchGenerateImage\referenceImages\1-20\naver\自然风景</t>
-  </si>
-  <si>
-    <t>D:\mog素材\待用素材库\naver自然背景</t>
-  </si>
-  <si>
-    <t>naver</t>
-  </si>
-  <si>
-    <t>kr</t>
-  </si>
-  <si>
-    <t>getAppAdsDesignerPrompt</t>
-  </si>
-  <si>
-    <t>combination2</t>
-  </si>
-  <si>
-    <t>logo+文字+图形组成画面，背景需要纯色就好可以有一些略微条纹变化</t>
-  </si>
-  <si>
-    <t>D:\batchGenerateImage\referenceImages\1-20\naver\纯logo排版</t>
-  </si>
-  <si>
-    <t>D:\mog素材\待用素材库\naver纯logo排版</t>
-  </si>
-  <si>
-    <t>地铁背景（线路图/实拍场景/地图）</t>
-  </si>
-  <si>
-    <t>D:\batchGenerateImage\referenceImages\1-20\naver\地铁线路背景</t>
-  </si>
-  <si>
-    <t>D:\mog素材\待用素材库\naver地铁线路背景</t>
-  </si>
-  <si>
-    <t>referenceImages/line</t>
-  </si>
-  <si>
-    <t>4:5</t>
-  </si>
-  <si>
-    <t>D:\mog素材\待用素材库\line竖2</t>
-  </si>
-  <si>
-    <t>line</t>
-  </si>
-  <si>
-    <t>getCutLogoPrompt</t>
   </si>
   <si>
     <t>getCentralPositionPrompt</t>
@@ -260,7 +339,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -425,6 +504,12 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -875,7 +960,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -902,6 +987,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1285,7 +1371,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="73.125" customWidth="1"/>
@@ -1392,12 +1478,15 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" ht="18" spans="1:14">
+    <row r="3" customFormat="1" ht="18" spans="1:14">
       <c r="A3" s="7"/>
       <c r="B3" t="s">
         <v>28</v>
       </c>
-      <c r="C3"/>
+      <c r="C3">
+        <v>0.5</v>
+      </c>
+      <c r="F3" s="6"/>
       <c r="G3" s="11" t="s">
         <v>29</v>
       </c>
@@ -1407,7 +1496,7 @@
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="8" t="s">
         <v>31</v>
       </c>
       <c r="K3" s="7" t="s">
@@ -1419,299 +1508,454 @@
       </c>
       <c r="N3" s="13"/>
     </row>
-    <row r="4" customFormat="1" ht="36" spans="1:14">
+    <row r="4" ht="18" spans="1:14">
       <c r="A4" s="7"/>
       <c r="B4" t="s">
         <v>34</v>
       </c>
       <c r="C4"/>
-      <c r="D4"/>
-      <c r="E4"/>
-      <c r="F4" s="6" t="s">
-        <v>35</v>
-      </c>
       <c r="G4" s="11" t="s">
         <v>29</v>
       </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L4" s="12"/>
+      <c r="M4" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="N4" s="13"/>
+    </row>
+    <row r="5" customFormat="1" ht="18" spans="1:14">
+      <c r="A5" s="7"/>
+      <c r="B5" t="s">
         <v>38</v>
       </c>
-      <c r="L4" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="M4" t="s">
-        <v>40</v>
-      </c>
-      <c r="N4" s="13"/>
-    </row>
-    <row r="5" customFormat="1" ht="36" customHeight="1" spans="1:14">
-      <c r="A5" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5">
-        <v>1.1</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>35</v>
-      </c>
+      <c r="F5" s="6"/>
       <c r="G5" s="11" t="s">
         <v>29</v>
       </c>
       <c r="H5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="K5" t="s">
-        <v>45</v>
-      </c>
-      <c r="L5" s="12" t="s">
-        <v>46</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="L5" s="12"/>
       <c r="M5" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="N5" s="13"/>
     </row>
-    <row r="6" customFormat="1" ht="36" customHeight="1" spans="1:14">
-      <c r="A6" s="7" t="s">
-        <v>48</v>
-      </c>
+    <row r="6" customFormat="1" ht="18" spans="1:14">
+      <c r="A6" s="7"/>
       <c r="B6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6">
-        <v>1.1</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>35</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F6" s="6"/>
       <c r="G6" s="11" t="s">
         <v>29</v>
       </c>
       <c r="H6" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="I6">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J6" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="L6" s="12"/>
+      <c r="M6" t="s">
+        <v>33</v>
+      </c>
+      <c r="N6" s="13"/>
+    </row>
+    <row r="7" customFormat="1" ht="36" spans="1:14">
+      <c r="A7" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
         <v>44</v>
       </c>
-      <c r="K6" t="s">
+      <c r="C7">
+        <v>1.5</v>
+      </c>
+      <c r="D7"/>
+      <c r="E7"/>
+      <c r="F7" s="6" t="s">
         <v>45</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="M6" t="s">
-        <v>47</v>
-      </c>
-      <c r="N6" s="13"/>
-    </row>
-    <row r="7" customFormat="1" ht="36" customHeight="1" spans="1:14">
-      <c r="A7" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7">
-        <v>1.1</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>35</v>
       </c>
       <c r="G7" s="11" t="s">
         <v>29</v>
       </c>
       <c r="H7" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="I7">
-        <v>15</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="K7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="M7" t="s">
+        <v>49</v>
+      </c>
+      <c r="N7" s="13"/>
+    </row>
+    <row r="8" customFormat="1" ht="36" spans="1:14">
+      <c r="A8" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8">
+        <v>1.5</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>45</v>
-      </c>
-      <c r="L7" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="M7" t="s">
-        <v>47</v>
-      </c>
-      <c r="N7" s="13"/>
-    </row>
-    <row r="8" customFormat="1" ht="54" spans="1:14">
-      <c r="A8" s="7"/>
-      <c r="B8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C8">
-        <v>0.5</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="G8" s="11" t="s">
         <v>29</v>
       </c>
       <c r="H8" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="K8" t="s">
-        <v>32</v>
-      </c>
-      <c r="L8" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="M8" t="s">
-        <v>40</v>
-      </c>
-      <c r="N8" s="13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" customFormat="1" ht="36" spans="1:14">
+        <v>15</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="M8"/>
+      <c r="N8" s="13"/>
+    </row>
+    <row r="9" customFormat="1" ht="36" customHeight="1" spans="1:14">
       <c r="A9" s="7" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C9">
         <v>1.8</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G9" s="11" t="s">
         <v>29</v>
       </c>
       <c r="H9" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="K9" t="s">
-        <v>38</v>
-      </c>
-      <c r="L9" s="13" t="s">
-        <v>64</v>
+        <v>36</v>
+      </c>
+      <c r="L9" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="M9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" customFormat="1" ht="36" spans="1:14">
-      <c r="A10" s="7"/>
+        <v>49</v>
+      </c>
+      <c r="N9" s="13"/>
+    </row>
+    <row r="10" customFormat="1" ht="36" customHeight="1" spans="1:14">
+      <c r="A10" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C10">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G10" s="11" t="s">
         <v>29</v>
       </c>
       <c r="H10" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K10" t="s">
         <v>32</v>
       </c>
-      <c r="L10" s="13" t="s">
-        <v>46</v>
+      <c r="L10" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="M10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" customFormat="1" ht="36" spans="1:14">
-      <c r="A11" s="7"/>
+        <v>49</v>
+      </c>
+      <c r="N10" s="13"/>
+    </row>
+    <row r="11" customFormat="1" ht="36" customHeight="1" spans="1:14">
+      <c r="A11" s="7" t="s">
+        <v>61</v>
+      </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C11">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>29</v>
       </c>
       <c r="H11" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="K11" t="s">
-        <v>38</v>
-      </c>
-      <c r="L11" s="13" t="s">
-        <v>59</v>
+        <v>41</v>
+      </c>
+      <c r="L11" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="M11" t="s">
+        <v>49</v>
+      </c>
+      <c r="N11" s="13"/>
+    </row>
+    <row r="12" customFormat="1" ht="36" customHeight="1" spans="1:14">
+      <c r="A12" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12">
+        <v>1.1</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" t="s">
+        <v>66</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12" s="8" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="19" spans="10:10">
-      <c r="J19" t="s">
+      <c r="K12" t="s">
+        <v>41</v>
+      </c>
+      <c r="L12" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="M12" t="s">
+        <v>49</v>
+      </c>
+      <c r="N12" s="13"/>
+    </row>
+    <row r="13" customFormat="1" ht="54" spans="1:14">
+      <c r="A13" s="7"/>
+      <c r="B13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13">
+        <v>0.5</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" t="s">
         <v>69</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="K13" t="s">
+        <v>36</v>
+      </c>
+      <c r="L13" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="M13" t="s">
+        <v>71</v>
+      </c>
+      <c r="N13" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" ht="36" spans="1:14">
+      <c r="A14" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14">
+        <v>1.8</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" t="s">
+        <v>75</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="K14" t="s">
+        <v>32</v>
+      </c>
+      <c r="L14" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="M14" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" ht="36" spans="1:14">
+      <c r="A15" s="7"/>
+      <c r="B15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15">
+        <v>1.1</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" t="s">
+        <v>78</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="K15" t="s">
+        <v>36</v>
+      </c>
+      <c r="L15" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="M15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" ht="36" spans="1:14">
+      <c r="A16" s="7"/>
+      <c r="B16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16">
+        <v>0.5</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" t="s">
+        <v>81</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="K16" t="s">
+        <v>32</v>
+      </c>
+      <c r="L16" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="M16" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="10:10">
+      <c r="J24" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3 G4 G5 G6 G7 G1:G2 G8:G11 G12:G1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F1:F2 F13:F1048576">
+      <formula1>Sheet3!$B$1:$B$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G1:G2 G13:G16 G17:G1048576">
       <formula1>Sheet3!$A$1:$A$10</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4 F5 F6 F7 F1:F3 F8:F1048576">
-      <formula1>Sheet3!$B$1:$B$10</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M4 M5 M6 M7 M1:M3 M8:M1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3 M4 M5 M6 M7 M8 M9 M10 M11 M12 M1:M2 M13:M1048576">
       <formula1>Sheet3!$C:$C</formula1>
     </dataValidation>
   </dataValidations>
@@ -1726,8 +1970,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4" outlineLevelCol="2"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="12.625" style="6"/>
     <col min="2" max="2" width="9" style="6"/>
@@ -1739,39 +1983,44 @@
         <v>29</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="6" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="B3" s="6" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="C4" s="7" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="C5" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="C6" s="7" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/config.xlsx
+++ b/config.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="87">
   <si>
     <t>提示词</t>
   </si>
@@ -115,16 +115,16 @@
     <t>nextPromptFun</t>
   </si>
   <si>
-    <t>D:\batchGenerateImage\referenceImages\1-20\gmail方竖</t>
+    <t>D:\batchGenerateImage\referenceImages\1-22\谷歌地图方竖</t>
   </si>
   <si>
     <t>1K</t>
   </si>
   <si>
-    <t>D:\mog素材\待用素材库\gmail方竖</t>
-  </si>
-  <si>
-    <t>gamil</t>
+    <t>D:\mog素材\待用素材库\0122谷歌地图方竖</t>
+  </si>
+  <si>
+    <t>谷歌地图</t>
   </si>
   <si>
     <t>us</t>
@@ -133,35 +133,38 @@
     <t>cut</t>
   </si>
   <si>
-    <t>D:\mog素材\xjt\gmail\0120-us</t>
-  </si>
-  <si>
-    <t>D:\mog素材\xjt\gmail\0120-jp</t>
-  </si>
-  <si>
-    <t>jp</t>
-  </si>
-  <si>
-    <t>translate</t>
-  </si>
-  <si>
-    <t>D:\batchGenerateImage\referenceImages\1-20\naver方竖\地铁线路背景</t>
-  </si>
-  <si>
-    <t>D:\mog素材\待用素材库\naver方竖</t>
-  </si>
-  <si>
-    <t>naver</t>
-  </si>
-  <si>
-    <t>kr</t>
-  </si>
-  <si>
-    <t>D:\batchGenerateImage\referenceImages\1-20\naver方竖\自然风景</t>
+    <t>D:\batchGenerateImage\referenceImages\1-22\谷歌邮箱方竖</t>
+  </si>
+  <si>
+    <t>D:\mog素材\待用素材库\0122谷歌邮箱方竖</t>
+  </si>
+  <si>
+    <t>谷歌邮箱</t>
+  </si>
+  <si>
+    <t>D:\batchGenerateImage\referenceImages\1-22\谷歌地图</t>
+  </si>
+  <si>
+    <t>16:9</t>
+  </si>
+  <si>
+    <t>D:\batchGenerateImage\data\googleMap</t>
+  </si>
+  <si>
+    <t>getAppDefaultPrompt</t>
+  </si>
+  <si>
+    <t>combination2</t>
+  </si>
+  <si>
+    <t>D:\batchGenerateImage\referenceImages\1-22\谷歌邮箱</t>
+  </si>
+  <si>
+    <t>D:\batchGenerateImage\data\gmail</t>
   </si>
   <si>
     <r>
-      <t>应用的图标跟参考图要保持一抹一样。</t>
+      <t>应用的图标跟参考图要保持一抹一样。要有**大脂金枪鱼（大トロ）**油脂发亮的特写，</t>
     </r>
     <r>
       <rPr>
@@ -170,58 +173,26 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>文案参考使用： 100円祭り開催中!或者</t>
+      <t>文案参考使用： 厳選ネタが、ぜんぶ110円</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>厳選ネタが、ぜんぶ110円</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 或者:売り切れ御免！はま寿司の100円祭り</t>
-    </r>
   </si>
   <si>
     <t>referenceImages/1-21/寿司</t>
   </si>
   <si>
-    <t>16:9</t>
-  </si>
-  <si>
     <t>D:\mog素材\待用素材库\1-21寿司</t>
   </si>
   <si>
     <t>はま寿司</t>
   </si>
   <si>
+    <t>jp</t>
+  </si>
+  <si>
     <t>getAppAdsDesignerPrompt</t>
   </si>
   <si>
-    <t>combination2</t>
-  </si>
-  <si>
-    <t>应用的图标跟参考图要保持一抹一样。根据参考图的结构构图更换不同人物以及背景</t>
+    <t>应用的图标跟参考图要保持一抹一样。根据参考图的结构构图更换不同人物以及樱花背景</t>
   </si>
   <si>
     <t>referenceImages/1-21/xjt寿司</t>
@@ -230,13 +201,13 @@
     <t>D:\mog素材\待用素材库\1-21xjt寿司</t>
   </si>
   <si>
-    <t>商务风格，背景简约</t>
-  </si>
-  <si>
-    <t>D:\batchGenerateImage\referenceImages\1-21\line商务感</t>
-  </si>
-  <si>
-    <t>D:\mog素材\待用素材库\1-21 line商务感</t>
+    <t>调整构图，并且应用图标右上角红点需要修改数值，背景需要为白粉渐变色稍微带一些写实樱花装饰</t>
+  </si>
+  <si>
+    <t>D:\batchGenerateImage\referenceImages\1-21\line樱花</t>
+  </si>
+  <si>
+    <t>D:\mog素材\待用素材库\1-21 line樱花</t>
   </si>
   <si>
     <t>line</t>
@@ -251,9 +222,6 @@
     <t>D:\mog素材\待用素材库\谷歌邮箱</t>
   </si>
   <si>
-    <t>谷歌邮箱</t>
-  </si>
-  <si>
     <t>logo+文字+图形组成画面，背景需要纯色就好可以有一些略微条纹变化</t>
   </si>
   <si>
@@ -263,6 +231,12 @@
     <t>D:\mog素材\待用素材库\naver纯logo排版</t>
   </si>
   <si>
+    <t>naver</t>
+  </si>
+  <si>
+    <t>kr</t>
+  </si>
+  <si>
     <t>地铁背景（线路图/实拍场景/地图）</t>
   </si>
   <si>
@@ -302,9 +276,6 @@
     <t>YouTube</t>
   </si>
   <si>
-    <t>getAppDefaultPrompt</t>
-  </si>
-  <si>
     <t>D:\mog素材\待用素材库\line</t>
   </si>
   <si>
@@ -327,6 +298,9 @@
   </si>
   <si>
     <t>combination3</t>
+  </si>
+  <si>
+    <t>translate</t>
   </si>
 </sst>
 </file>
@@ -1513,7 +1487,9 @@
       <c r="B4" t="s">
         <v>34</v>
       </c>
-      <c r="C4"/>
+      <c r="C4">
+        <v>0.5</v>
+      </c>
       <c r="G4" s="11" t="s">
         <v>29</v>
       </c>
@@ -1521,26 +1497,28 @@
         <v>35</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="L4" s="12"/>
       <c r="M4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N4" s="13"/>
     </row>
-    <row r="5" customFormat="1" ht="18" spans="1:14">
+    <row r="5" customFormat="1" ht="36" spans="1:14">
       <c r="A5" s="7"/>
       <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="6"/>
       <c r="G5" s="11" t="s">
         <v>29</v>
       </c>
@@ -1551,50 +1529,56 @@
         <v>0</v>
       </c>
       <c r="J5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="M5" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="12"/>
-      <c r="M5" t="s">
-        <v>33</v>
-      </c>
       <c r="N5" s="13"/>
     </row>
-    <row r="6" customFormat="1" ht="18" spans="1:14">
+    <row r="6" customFormat="1" ht="36" spans="1:14">
       <c r="A6" s="7"/>
       <c r="B6" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="6"/>
+      <c r="F6" s="6" t="s">
+        <v>38</v>
+      </c>
       <c r="G6" s="11" t="s">
         <v>29</v>
       </c>
       <c r="H6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="M6" t="s">
         <v>41</v>
-      </c>
-      <c r="L6" s="12"/>
-      <c r="M6" t="s">
-        <v>33</v>
       </c>
       <c r="N6" s="13"/>
     </row>
     <row r="7" customFormat="1" ht="36" spans="1:14">
       <c r="A7" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7">
         <v>1.5</v>
@@ -1602,7 +1586,7 @@
       <c r="D7"/>
       <c r="E7"/>
       <c r="F7" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G7" s="11" t="s">
         <v>29</v>
@@ -1611,20 +1595,18 @@
         <v>46</v>
       </c>
       <c r="I7">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J7" s="7" t="s">
         <v>47</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="M7" t="s">
         <v>49</v>
       </c>
+      <c r="M7"/>
       <c r="N7" s="13"/>
     </row>
     <row r="8" customFormat="1" ht="36" spans="1:14">
@@ -1635,10 +1617,10 @@
         <v>51</v>
       </c>
       <c r="C8">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G8" s="11" t="s">
         <v>29</v>
@@ -1647,16 +1629,16 @@
         <v>52</v>
       </c>
       <c r="I8">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J8" s="7" t="s">
         <v>47</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M8"/>
       <c r="N8" s="13"/>
@@ -1669,10 +1651,10 @@
         <v>54</v>
       </c>
       <c r="C9">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G9" s="11" t="s">
         <v>29</v>
@@ -1681,19 +1663,19 @@
         <v>55</v>
       </c>
       <c r="I9">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J9" s="8" t="s">
         <v>56</v>
       </c>
       <c r="K9" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="L9" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M9" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="N9" s="13"/>
     </row>
@@ -1708,7 +1690,7 @@
         <v>1.8</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G10" s="11" t="s">
         <v>29</v>
@@ -1720,107 +1702,107 @@
         <v>0</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="K10" t="s">
         <v>32</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M10" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="N10" s="13"/>
     </row>
     <row r="11" customFormat="1" ht="36" customHeight="1" spans="1:14">
       <c r="A11" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
         <v>61</v>
-      </c>
-      <c r="B11" t="s">
-        <v>62</v>
       </c>
       <c r="C11">
         <v>1.1</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>29</v>
       </c>
       <c r="H11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="K11" t="s">
+        <v>64</v>
+      </c>
+      <c r="L11" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="M11" t="s">
         <v>41</v>
-      </c>
-      <c r="L11" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="M11" t="s">
-        <v>49</v>
       </c>
       <c r="N11" s="13"/>
     </row>
     <row r="12" customFormat="1" ht="36" customHeight="1" spans="1:14">
       <c r="A12" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C12">
         <v>1.1</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G12" s="11" t="s">
         <v>29</v>
       </c>
       <c r="H12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="K12" t="s">
+        <v>64</v>
+      </c>
+      <c r="L12" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="M12" t="s">
         <v>41</v>
-      </c>
-      <c r="L12" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="M12" t="s">
-        <v>49</v>
       </c>
       <c r="N12" s="13"/>
     </row>
     <row r="13" customFormat="1" ht="54" spans="1:14">
       <c r="A13" s="7"/>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C13">
         <v>0.5</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G13" s="11" t="s">
         <v>29</v>
       </c>
       <c r="H13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1829,63 +1811,63 @@
         <v>56</v>
       </c>
       <c r="K13" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" customFormat="1" ht="36" spans="1:14">
       <c r="A14" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C14">
         <v>1.8</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G14" s="11" t="s">
         <v>29</v>
       </c>
       <c r="H14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K14" t="s">
         <v>32</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="M14" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" customFormat="1" ht="36" spans="1:14">
       <c r="A15" s="7"/>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C15">
         <v>1.1</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G15" s="11" t="s">
         <v>29</v>
@@ -1900,13 +1882,13 @@
         <v>56</v>
       </c>
       <c r="K15" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="L15" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M15" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" customFormat="1" ht="36" spans="1:14">
@@ -1930,16 +1912,16 @@
         <v>0</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K16" t="s">
         <v>32</v>
       </c>
       <c r="L16" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="M16" t="s">
         <v>72</v>
-      </c>
-      <c r="M16" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="24" spans="10:10">
@@ -1986,7 +1968,7 @@
         <v>80</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1994,7 +1976,7 @@
         <v>83</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>84</v>
@@ -2002,10 +1984,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="B3" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2020,7 +2002,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="C6" s="7" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/config.xlsx
+++ b/config.xlsx
@@ -1497,7 +1497,7 @@
         <v>35</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>36</v>

--- a/config.xlsx
+++ b/config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="31290" windowHeight="10725"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="94">
   <si>
     <t>提示词</t>
   </si>
@@ -115,16 +115,16 @@
     <t>nextPromptFun</t>
   </si>
   <si>
-    <t>D:\batchGenerateImage\referenceImages\1-22\谷歌地图方竖</t>
+    <t>D:\batchGenerateImage\referenceImages\1-23\kakaotalk方竖</t>
   </si>
   <si>
     <t>1K</t>
   </si>
   <si>
-    <t>D:\mog素材\待用素材库\0122谷歌地图方竖</t>
-  </si>
-  <si>
-    <t>谷歌地图</t>
+    <t>D:\mog素材\待用素材库\0123kakaotalk方竖</t>
+  </si>
+  <si>
+    <t>kakaotalk</t>
   </si>
   <si>
     <t>us</t>
@@ -133,37 +133,71 @@
     <t>cut</t>
   </si>
   <si>
-    <t>D:\batchGenerateImage\referenceImages\1-22\谷歌邮箱方竖</t>
-  </si>
-  <si>
-    <t>D:\mog素材\待用素材库\0122谷歌邮箱方竖</t>
-  </si>
-  <si>
-    <t>谷歌邮箱</t>
-  </si>
-  <si>
-    <t>D:\batchGenerateImage\referenceImages\1-22\谷歌地图</t>
+    <t>D:\batchGenerateImage\referenceImages\1-23\naver方竖</t>
+  </si>
+  <si>
+    <t>D:\mog素材\待用素材库\0123naver方竖</t>
+  </si>
+  <si>
+    <t>naver</t>
+  </si>
+  <si>
+    <t>D:\batchGenerateImage\referenceImages\1-23\YouTube方竖</t>
+  </si>
+  <si>
+    <t>D:\mog素材\待用素材库\0123YouTube方竖</t>
+  </si>
+  <si>
+    <t>YouTube</t>
+  </si>
+  <si>
+    <t>D:\batchGenerateImage\referenceImages\1-23\kakaotalk</t>
   </si>
   <si>
     <t>16:9</t>
   </si>
   <si>
-    <t>D:\batchGenerateImage\data\googleMap</t>
-  </si>
-  <si>
-    <t>getAppDefaultPrompt</t>
+    <t>D:\batchGenerateImage\data\kakaotalk</t>
+  </si>
+  <si>
+    <t>kr</t>
+  </si>
+  <si>
+    <t>getAppAdsDesignerPrompt</t>
   </si>
   <si>
     <t>combination2</t>
   </si>
   <si>
-    <t>D:\batchGenerateImage\referenceImages\1-22\谷歌邮箱</t>
-  </si>
-  <si>
-    <t>D:\batchGenerateImage\data\gmail</t>
+    <t>D:\batchGenerateImage\referenceImages\1-23\naver</t>
+  </si>
+  <si>
+    <t>D:\batchGenerateImage\data\naver</t>
+  </si>
+  <si>
+    <t>D:\batchGenerateImage\referenceImages\1-23\YouTube</t>
+  </si>
+  <si>
+    <t>D:\batchGenerateImage\data\youtube</t>
+  </si>
+  <si>
+    <t>youtube</t>
+  </si>
+  <si>
+    <t>D:\batchGenerateImage\data\youtube\jp</t>
+  </si>
+  <si>
+    <t>jp</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>应用的图标跟参考图要保持一抹一样。要有**大脂金枪鱼（大トロ）**油脂发亮的特写，</t>
     </r>
     <r>
@@ -186,12 +220,6 @@
     <t>はま寿司</t>
   </si>
   <si>
-    <t>jp</t>
-  </si>
-  <si>
-    <t>getAppAdsDesignerPrompt</t>
-  </si>
-  <si>
     <t>应用的图标跟参考图要保持一抹一样。根据参考图的结构构图更换不同人物以及樱花背景</t>
   </si>
   <si>
@@ -222,6 +250,9 @@
     <t>D:\mog素材\待用素材库\谷歌邮箱</t>
   </si>
   <si>
+    <t>谷歌邮箱</t>
+  </si>
+  <si>
     <t>logo+文字+图形组成画面，背景需要纯色就好可以有一些略微条纹变化</t>
   </si>
   <si>
@@ -231,12 +262,6 @@
     <t>D:\mog素材\待用素材库\naver纯logo排版</t>
   </si>
   <si>
-    <t>naver</t>
-  </si>
-  <si>
-    <t>kr</t>
-  </si>
-  <si>
     <t>地铁背景（线路图/实拍场景/地图）</t>
   </si>
   <si>
@@ -273,7 +298,7 @@
     <t>D:\mog素材\待用素材库\YouTube</t>
   </si>
   <si>
-    <t>YouTube</t>
+    <t>getAppDefaultPrompt</t>
   </si>
   <si>
     <t>D:\mog素材\待用素材库\line</t>
@@ -295,6 +320,9 @@
   </si>
   <si>
     <t>combination</t>
+  </si>
+  <si>
+    <t>9:16</t>
   </si>
   <si>
     <t>combination3</t>
@@ -934,7 +962,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -954,10 +982,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1345,7 +1369,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="73.125" customWidth="1"/>
@@ -1461,14 +1485,14 @@
         <v>0.5</v>
       </c>
       <c r="F3" s="6"/>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H3" t="s">
         <v>30</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>31</v>
@@ -1476,11 +1500,11 @@
       <c r="K3" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="12"/>
+      <c r="L3" s="11"/>
       <c r="M3" t="s">
         <v>33</v>
       </c>
-      <c r="N3" s="13"/>
+      <c r="N3" s="11"/>
     </row>
     <row r="4" ht="18" spans="1:14">
       <c r="A4" s="7"/>
@@ -1490,14 +1514,14 @@
       <c r="C4">
         <v>0.5</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H4" t="s">
         <v>35</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>36</v>
@@ -1505,270 +1529,266 @@
       <c r="K4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L4" s="12"/>
+      <c r="L4" s="11"/>
       <c r="M4" t="s">
         <v>33</v>
       </c>
-      <c r="N4" s="13"/>
-    </row>
-    <row r="5" customFormat="1" ht="36" spans="1:14">
+      <c r="N4" s="11"/>
+    </row>
+    <row r="5" customFormat="1" ht="18" spans="1:14">
       <c r="A5" s="7"/>
       <c r="B5" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="C5">
+        <v>0.5</v>
+      </c>
+      <c r="F5" s="6"/>
+      <c r="G5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5" s="8" t="s">
         <v>39</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>31</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L5" s="12" t="s">
-        <v>40</v>
-      </c>
+      <c r="L5" s="11"/>
       <c r="M5" t="s">
-        <v>41</v>
-      </c>
-      <c r="N5" s="13"/>
+        <v>33</v>
+      </c>
+      <c r="N5" s="11"/>
     </row>
     <row r="6" customFormat="1" ht="36" spans="1:14">
       <c r="A6" s="7"/>
       <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6">
+        <v>1.1</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" t="s">
         <v>42</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" t="s">
-        <v>43</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>40</v>
+        <v>43</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>44</v>
       </c>
       <c r="M6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N6" s="11"/>
+    </row>
+    <row r="7" customFormat="1" ht="36" spans="1:14">
+      <c r="A7" s="7"/>
+      <c r="B7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7">
+        <v>1.1</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="N6" s="13"/>
-    </row>
-    <row r="7" customFormat="1" ht="36" spans="1:14">
-      <c r="A7" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7">
-        <v>1.5</v>
-      </c>
-      <c r="D7"/>
-      <c r="E7"/>
-      <c r="F7" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7" s="7" t="s">
-        <v>47</v>
+      <c r="J7" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="K7" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M7" t="s">
+        <v>45</v>
+      </c>
+      <c r="N7" s="11"/>
+    </row>
+    <row r="8" customFormat="1" ht="36" spans="1:14">
+      <c r="A8" s="7"/>
+      <c r="B8" t="s">
         <v>48</v>
-      </c>
-      <c r="L7" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="M7"/>
-      <c r="N7" s="13"/>
-    </row>
-    <row r="8" customFormat="1" ht="36" spans="1:14">
-      <c r="A8" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" t="s">
-        <v>51</v>
       </c>
       <c r="C8">
         <v>1.1</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H8" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8">
+        <v>15</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M8" t="s">
+        <v>45</v>
+      </c>
+      <c r="N8" s="11"/>
+    </row>
+    <row r="9" customFormat="1" ht="36" spans="1:14">
+      <c r="A9" s="7"/>
+      <c r="B9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9">
+        <v>1.1</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" t="s">
+        <v>51</v>
+      </c>
+      <c r="I9">
+        <v>15</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="K9" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="L8" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="M8"/>
-      <c r="N8" s="13"/>
-    </row>
-    <row r="9" customFormat="1" ht="36" customHeight="1" spans="1:14">
-      <c r="A9" s="7" t="s">
+      <c r="L9" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M9" t="s">
+        <v>45</v>
+      </c>
+      <c r="N9" s="11"/>
+    </row>
+    <row r="10" customFormat="1" ht="36" spans="1:14">
+      <c r="A10" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B10" t="s">
         <v>54</v>
       </c>
-      <c r="C9">
+      <c r="C10">
         <v>1.5</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" s="11" t="s">
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H10" t="s">
         <v>55</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="K9" t="s">
-        <v>48</v>
-      </c>
-      <c r="L9" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="M9" t="s">
-        <v>41</v>
-      </c>
-      <c r="N9" s="13"/>
-    </row>
-    <row r="10" customFormat="1" ht="36" customHeight="1" spans="1:14">
-      <c r="A10" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10">
-        <v>1.8</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10" t="s">
-        <v>59</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
-      <c r="J10" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="K10" t="s">
-        <v>32</v>
-      </c>
-      <c r="L10" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="M10" t="s">
-        <v>41</v>
-      </c>
-      <c r="N10" s="13"/>
-    </row>
-    <row r="11" customFormat="1" ht="36" customHeight="1" spans="1:14">
-      <c r="A11" s="7" t="s">
-        <v>60</v>
+      <c r="J10" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M10"/>
+      <c r="N10" s="11"/>
+    </row>
+    <row r="11" customFormat="1" ht="36" spans="1:14">
+      <c r="A11" s="12" t="s">
+        <v>57</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C11">
         <v>1.1</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H11" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
-      <c r="J11" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="K11" t="s">
-        <v>64</v>
-      </c>
-      <c r="L11" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="M11" t="s">
-        <v>41</v>
-      </c>
-      <c r="N11" s="13"/>
+      <c r="J11" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M11"/>
+      <c r="N11" s="11"/>
     </row>
     <row r="12" customFormat="1" ht="36" customHeight="1" spans="1:14">
       <c r="A12" s="7" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C12">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G12" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H12" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1777,174 +1797,282 @@
         <v>63</v>
       </c>
       <c r="K12" t="s">
+        <v>52</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M12" t="s">
+        <v>45</v>
+      </c>
+      <c r="N12" s="11"/>
+    </row>
+    <row r="13" customFormat="1" ht="36" customHeight="1" spans="1:14">
+      <c r="A13" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="L12" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="M12" t="s">
+      <c r="B13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13">
+        <v>1.8</v>
+      </c>
+      <c r="F13" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="N12" s="13"/>
-    </row>
-    <row r="13" customFormat="1" ht="54" spans="1:14">
-      <c r="A13" s="7"/>
-      <c r="B13" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13">
-        <v>0.5</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H13" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="K13" t="s">
-        <v>48</v>
-      </c>
-      <c r="L13" s="13" t="s">
-        <v>71</v>
+        <v>32</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>44</v>
       </c>
       <c r="M13" t="s">
-        <v>72</v>
-      </c>
-      <c r="N13" s="13" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="14" customFormat="1" ht="36" spans="1:14">
+        <v>45</v>
+      </c>
+      <c r="N13" s="11"/>
+    </row>
+    <row r="14" customFormat="1" ht="36" customHeight="1" spans="1:14">
       <c r="A14" s="7" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C14">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G14" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H14" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="K14" t="s">
-        <v>32</v>
-      </c>
-      <c r="L14" s="13" t="s">
-        <v>40</v>
+        <v>43</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>44</v>
       </c>
       <c r="M14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" customFormat="1" ht="36" spans="1:14">
-      <c r="A15" s="7"/>
+        <v>45</v>
+      </c>
+      <c r="N14" s="11"/>
+    </row>
+    <row r="15" customFormat="1" ht="36" customHeight="1" spans="1:14">
+      <c r="A15" s="7" t="s">
+        <v>71</v>
+      </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C15">
         <v>1.1</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G15" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H15" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="K15" t="s">
-        <v>48</v>
-      </c>
-      <c r="L15" s="13" t="s">
-        <v>49</v>
+        <v>43</v>
+      </c>
+      <c r="L15" s="11" t="s">
+        <v>44</v>
       </c>
       <c r="M15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" customFormat="1" ht="36" spans="1:14">
+        <v>45</v>
+      </c>
+      <c r="N15" s="11"/>
+    </row>
+    <row r="16" customFormat="1" ht="54" spans="1:14">
       <c r="A16" s="7"/>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C16">
         <v>0.5</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="G16" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H16" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="K16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L16" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="K16" t="s">
+      <c r="M16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N16" s="11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" ht="36" spans="1:13">
+      <c r="A17" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17">
+        <v>1.8</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" t="s">
+        <v>82</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="K17" t="s">
         <v>32</v>
       </c>
-      <c r="L16" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="M16" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="24" spans="10:10">
-      <c r="J24" t="s">
-        <v>82</v>
+      <c r="L17" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="M17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" ht="36" spans="1:13">
+      <c r="A18" s="7"/>
+      <c r="B18" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18">
+        <v>1.1</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" t="s">
+        <v>84</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="K18" t="s">
+        <v>52</v>
+      </c>
+      <c r="L18" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" ht="36" spans="1:13">
+      <c r="A19" s="7"/>
+      <c r="B19" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19">
+        <v>0.5</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H19" t="s">
+        <v>87</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="K19" t="s">
+        <v>32</v>
+      </c>
+      <c r="L19" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="M19" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="J27" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F1:F2 F13:F1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5 F6 F7 F8 F9 F1:F4 F10:F1048576">
       <formula1>Sheet3!$B$1:$B$10</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G1:G2 G13:G16 G17:G1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5 G6 G7 G8 G9 G1:G4 G10:G1048576">
       <formula1>Sheet3!$A$1:$A$10</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3 M4 M5 M6 M7 M8 M9 M10 M11 M12 M1:M2 M13:M1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M5 M6 M7 M8 M9 M1:M4 M10:M1048576">
       <formula1>Sheet3!$C:$C</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C2:E2 D1:I1 A1:B1 A2 G2" numberStoredAsText="1"/>
+    <ignoredError sqref="G2 A2 A1:B1 D1:I1 C2:E2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1965,34 +2093,37 @@
         <v>29</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="6" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="B3" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:3">
+      <c r="B4" s="6" t="s">
+        <v>91</v>
+      </c>
       <c r="C4" s="7" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2002,7 +2133,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="C6" s="7" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/config.xlsx
+++ b/config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="95">
   <si>
     <t>提示词</t>
   </si>
@@ -149,6 +149,9 @@
   </si>
   <si>
     <t>YouTube</t>
+  </si>
+  <si>
+    <t>桌上两杯拉花拿铁和一小块精致糕点，杯子与餐具精致，微俯拍，中景，桌子与店内装修符合咖啡店的温暖氛围，背景稍微显露咖啡店精致环境，画面整体干净协调，符合韩国人审美</t>
   </si>
   <si>
     <t>D:\batchGenerateImage\referenceImages\1-23\kakaotalk</t>
@@ -1492,7 +1495,7 @@
         <v>30</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>31</v>
@@ -1521,7 +1524,7 @@
         <v>35</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>36</v>
@@ -1551,7 +1554,7 @@
         <v>38</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J5" s="8" t="s">
         <v>39</v>
@@ -1566,21 +1569,23 @@
       <c r="N5" s="11"/>
     </row>
     <row r="6" customFormat="1" ht="36" spans="1:14">
-      <c r="A6" s="7"/>
+      <c r="A6" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C6">
         <v>1.1</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1589,32 +1594,32 @@
         <v>31</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N6" s="11"/>
     </row>
     <row r="7" customFormat="1" ht="36" spans="1:14">
       <c r="A7" s="7"/>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C7">
         <v>1.1</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1623,90 +1628,90 @@
         <v>36</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N7" s="11"/>
     </row>
     <row r="8" customFormat="1" ht="36" spans="1:14">
       <c r="A8" s="7"/>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C8">
         <v>1.1</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I8">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>32</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N8" s="11"/>
     </row>
     <row r="9" customFormat="1" ht="36" spans="1:14">
       <c r="A9" s="7"/>
       <c r="B9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C9">
         <v>1.1</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H9" t="s">
+        <v>52</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="I9">
-        <v>15</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>50</v>
-      </c>
       <c r="K9" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N9" s="11"/>
     </row>
     <row r="10" customFormat="1" ht="36" spans="1:14">
       <c r="A10" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C10">
         <v>1.5</v>
@@ -1714,153 +1719,153 @@
       <c r="D10"/>
       <c r="E10"/>
       <c r="F10" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M10"/>
       <c r="N10" s="11"/>
     </row>
     <row r="11" customFormat="1" ht="36" spans="1:14">
       <c r="A11" s="12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C11">
         <v>1.1</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M11"/>
       <c r="N11" s="11"/>
     </row>
     <row r="12" customFormat="1" ht="36" customHeight="1" spans="1:14">
       <c r="A12" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C12">
         <v>1.5</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N12" s="11"/>
     </row>
     <row r="13" customFormat="1" ht="36" customHeight="1" spans="1:14">
       <c r="A13" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C13">
         <v>1.8</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K13" t="s">
         <v>32</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N13" s="11"/>
     </row>
     <row r="14" customFormat="1" ht="36" customHeight="1" spans="1:14">
       <c r="A14" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C14">
         <v>1.1</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1869,34 +1874,34 @@
         <v>36</v>
       </c>
       <c r="K14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N14" s="11"/>
     </row>
     <row r="15" customFormat="1" ht="36" customHeight="1" spans="1:14">
       <c r="A15" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C15">
         <v>1.1</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1905,70 +1910,70 @@
         <v>36</v>
       </c>
       <c r="K15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N15" s="11"/>
     </row>
     <row r="16" customFormat="1" ht="54" spans="1:14">
       <c r="A16" s="7"/>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C16">
         <v>0.5</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N16" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" customFormat="1" ht="36" spans="1:13">
       <c r="A17" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C17">
         <v>1.8</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1980,61 +1985,61 @@
         <v>32</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" customFormat="1" ht="36" spans="1:13">
       <c r="A18" s="7"/>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C18">
         <v>1.1</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" customFormat="1" ht="36" spans="1:13">
       <c r="A19" s="7"/>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C19">
         <v>0.5</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -2046,15 +2051,15 @@
         <v>32</v>
       </c>
       <c r="L19" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="M19" t="s">
         <v>79</v>
-      </c>
-      <c r="M19" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:13">
       <c r="J27" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -2093,37 +2098,37 @@
         <v>29</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="B3" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="B4" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2133,7 +2138,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="C6" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/config.xlsx
+++ b/config.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="95">
   <si>
     <t>提示词</t>
   </si>
@@ -151,16 +151,13 @@
     <t>YouTube</t>
   </si>
   <si>
-    <t>桌上两杯拉花拿铁和一小块精致糕点，杯子与餐具精致，微俯拍，中景，桌子与店内装修符合咖啡店的温暖氛围，背景稍微显露咖啡店精致环境，画面整体干净协调，符合韩国人审美</t>
-  </si>
-  <si>
-    <t>D:\batchGenerateImage\referenceImages\1-23\kakaotalk</t>
+    <t>D:\batchGenerateImage\referenceImages\1-26\naver</t>
   </si>
   <si>
     <t>16:9</t>
   </si>
   <si>
-    <t>D:\batchGenerateImage\data\kakaotalk</t>
+    <t>D:\batchGenerateImage\data\naver</t>
   </si>
   <si>
     <t>kr</t>
@@ -172,10 +169,13 @@
     <t>combination2</t>
   </si>
   <si>
-    <t>D:\batchGenerateImage\referenceImages\1-23\naver</t>
-  </si>
-  <si>
-    <t>D:\batchGenerateImage\data\naver</t>
+    <t>D:\batchGenerateImage\referenceImages\1-26\谷歌地图</t>
+  </si>
+  <si>
+    <t>D:\batchGenerateImage\data\gmailMap</t>
+  </si>
+  <si>
+    <t>谷歌地图</t>
   </si>
   <si>
     <t>D:\batchGenerateImage\referenceImages\1-23\YouTube</t>
@@ -1569,72 +1569,70 @@
       <c r="N5" s="11"/>
     </row>
     <row r="6" customFormat="1" ht="36" spans="1:14">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="7"/>
+      <c r="B6" t="s">
         <v>40</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6">
+        <v>1.5</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="C6">
-        <v>1.1</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>42</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6">
+        <v>15</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="K6" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="K6" s="7" t="s">
+      <c r="L6" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="M6" t="s">
         <v>45</v>
-      </c>
-      <c r="M6" t="s">
-        <v>46</v>
       </c>
       <c r="N6" s="11"/>
     </row>
     <row r="7" customFormat="1" ht="36" spans="1:14">
       <c r="A7" s="7"/>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C7">
         <v>1.1</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7">
+        <v>20</v>
+      </c>
+      <c r="J7" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>36</v>
-      </c>
       <c r="K7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="L7" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="L7" s="11" t="s">
+      <c r="M7" t="s">
         <v>45</v>
-      </c>
-      <c r="M7" t="s">
-        <v>46</v>
       </c>
       <c r="N7" s="11"/>
     </row>
@@ -1647,7 +1645,7 @@
         <v>1.1</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>29</v>
@@ -1665,10 +1663,10 @@
         <v>32</v>
       </c>
       <c r="L8" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M8" t="s">
         <v>45</v>
-      </c>
-      <c r="M8" t="s">
-        <v>46</v>
       </c>
       <c r="N8" s="11"/>
     </row>
@@ -1681,7 +1679,7 @@
         <v>1.1</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>29</v>
@@ -1699,10 +1697,10 @@
         <v>53</v>
       </c>
       <c r="L9" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M9" t="s">
         <v>45</v>
-      </c>
-      <c r="M9" t="s">
-        <v>46</v>
       </c>
       <c r="N9" s="11"/>
     </row>
@@ -1719,7 +1717,7 @@
       <c r="D10"/>
       <c r="E10"/>
       <c r="F10" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>29</v>
@@ -1737,7 +1735,7 @@
         <v>53</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M10"/>
       <c r="N10" s="11"/>
@@ -1753,7 +1751,7 @@
         <v>1.1</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>29</v>
@@ -1771,7 +1769,7 @@
         <v>53</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M11"/>
       <c r="N11" s="11"/>
@@ -1787,7 +1785,7 @@
         <v>1.5</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>29</v>
@@ -1805,10 +1803,10 @@
         <v>53</v>
       </c>
       <c r="L12" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M12" t="s">
         <v>45</v>
-      </c>
-      <c r="M12" t="s">
-        <v>46</v>
       </c>
       <c r="N12" s="11"/>
     </row>
@@ -1823,7 +1821,7 @@
         <v>1.8</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>29</v>
@@ -1841,10 +1839,10 @@
         <v>32</v>
       </c>
       <c r="L13" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M13" t="s">
         <v>45</v>
-      </c>
-      <c r="M13" t="s">
-        <v>46</v>
       </c>
       <c r="N13" s="11"/>
     </row>
@@ -1859,7 +1857,7 @@
         <v>1.1</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>29</v>
@@ -1874,13 +1872,13 @@
         <v>36</v>
       </c>
       <c r="K14" t="s">
+        <v>43</v>
+      </c>
+      <c r="L14" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="L14" s="11" t="s">
+      <c r="M14" t="s">
         <v>45</v>
-      </c>
-      <c r="M14" t="s">
-        <v>46</v>
       </c>
       <c r="N14" s="11"/>
     </row>
@@ -1895,7 +1893,7 @@
         <v>1.1</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>29</v>
@@ -1910,13 +1908,13 @@
         <v>36</v>
       </c>
       <c r="K15" t="s">
+        <v>43</v>
+      </c>
+      <c r="L15" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="L15" s="11" t="s">
+      <c r="M15" t="s">
         <v>45</v>
-      </c>
-      <c r="M15" t="s">
-        <v>46</v>
       </c>
       <c r="N15" s="11"/>
     </row>
@@ -1967,7 +1965,7 @@
         <v>1.8</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>29</v>
@@ -1988,7 +1986,7 @@
         <v>84</v>
       </c>
       <c r="M17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" customFormat="1" ht="36" spans="1:13">
@@ -2000,7 +1998,7 @@
         <v>1.1</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>29</v>
@@ -2018,10 +2016,10 @@
         <v>53</v>
       </c>
       <c r="L18" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M18" t="s">
         <v>45</v>
-      </c>
-      <c r="M18" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="19" customFormat="1" ht="36" spans="1:13">
@@ -2117,10 +2115,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="B3" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:3">

--- a/config.xlsx
+++ b/config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="94">
   <si>
     <t>提示词</t>
   </si>
@@ -115,16 +115,16 @@
     <t>nextPromptFun</t>
   </si>
   <si>
-    <t>D:\batchGenerateImage\referenceImages\1-23\kakaotalk方竖</t>
+    <t>D:\batchGenerateImage\referenceImages\1-26\谷歌地图方竖</t>
   </si>
   <si>
     <t>1K</t>
   </si>
   <si>
-    <t>D:\mog素材\待用素材库\0123kakaotalk方竖</t>
-  </si>
-  <si>
-    <t>kakaotalk</t>
+    <t>D:\mog素材\待用素材库\0126谷歌地图方竖</t>
+  </si>
+  <si>
+    <t>谷歌地图</t>
   </si>
   <si>
     <t>us</t>
@@ -133,10 +133,10 @@
     <t>cut</t>
   </si>
   <si>
-    <t>D:\batchGenerateImage\referenceImages\1-23\naver方竖</t>
-  </si>
-  <si>
-    <t>D:\mog素材\待用素材库\0123naver方竖</t>
+    <t>D:\batchGenerateImage\referenceImages\1-26\naver方竖</t>
+  </si>
+  <si>
+    <t>D:\mog素材\待用素材库\0126naver方竖</t>
   </si>
   <si>
     <t>naver</t>
@@ -172,10 +172,7 @@
     <t>D:\batchGenerateImage\referenceImages\1-26\谷歌地图</t>
   </si>
   <si>
-    <t>D:\batchGenerateImage\data\gmailMap</t>
-  </si>
-  <si>
-    <t>谷歌地图</t>
+    <t>D:\batchGenerateImage\data\googleMap</t>
   </si>
   <si>
     <t>D:\batchGenerateImage\referenceImages\1-23\YouTube</t>
@@ -1495,7 +1492,7 @@
         <v>30</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>31</v>
@@ -1524,7 +1521,7 @@
         <v>35</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>36</v>
@@ -1574,7 +1571,7 @@
         <v>40</v>
       </c>
       <c r="C6">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>41</v>
@@ -1586,7 +1583,7 @@
         <v>42</v>
       </c>
       <c r="I6">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J6" s="8" t="s">
         <v>36</v>
@@ -1620,10 +1617,10 @@
         <v>47</v>
       </c>
       <c r="I7">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>32</v>
@@ -1639,7 +1636,7 @@
     <row r="8" customFormat="1" ht="36" spans="1:14">
       <c r="A8" s="7"/>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C8">
         <v>1.1</v>
@@ -1651,13 +1648,13 @@
         <v>29</v>
       </c>
       <c r="H8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>32</v>
@@ -1673,7 +1670,7 @@
     <row r="9" customFormat="1" ht="36" spans="1:14">
       <c r="A9" s="7"/>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C9">
         <v>1.1</v>
@@ -1685,16 +1682,16 @@
         <v>29</v>
       </c>
       <c r="H9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L9" s="11" t="s">
         <v>44</v>
@@ -1706,10 +1703,10 @@
     </row>
     <row r="10" customFormat="1" ht="36" spans="1:14">
       <c r="A10" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
         <v>54</v>
-      </c>
-      <c r="B10" t="s">
-        <v>55</v>
       </c>
       <c r="C10">
         <v>1.5</v>
@@ -1723,16 +1720,16 @@
         <v>29</v>
       </c>
       <c r="H10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L10" s="11" t="s">
         <v>44</v>
@@ -1742,10 +1739,10 @@
     </row>
     <row r="11" customFormat="1" ht="36" spans="1:14">
       <c r="A11" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" t="s">
         <v>58</v>
-      </c>
-      <c r="B11" t="s">
-        <v>59</v>
       </c>
       <c r="C11">
         <v>1.1</v>
@@ -1757,16 +1754,16 @@
         <v>29</v>
       </c>
       <c r="H11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L11" s="11" t="s">
         <v>44</v>
@@ -1776,10 +1773,10 @@
     </row>
     <row r="12" customFormat="1" ht="36" customHeight="1" spans="1:14">
       <c r="A12" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" t="s">
         <v>61</v>
-      </c>
-      <c r="B12" t="s">
-        <v>62</v>
       </c>
       <c r="C12">
         <v>1.5</v>
@@ -1791,16 +1788,16 @@
         <v>29</v>
       </c>
       <c r="H12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L12" s="11" t="s">
         <v>44</v>
@@ -1812,10 +1809,10 @@
     </row>
     <row r="13" customFormat="1" ht="36" customHeight="1" spans="1:14">
       <c r="A13" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" t="s">
         <v>65</v>
-      </c>
-      <c r="B13" t="s">
-        <v>66</v>
       </c>
       <c r="C13">
         <v>1.8</v>
@@ -1827,13 +1824,13 @@
         <v>29</v>
       </c>
       <c r="H13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K13" t="s">
         <v>32</v>
@@ -1848,10 +1845,10 @@
     </row>
     <row r="14" customFormat="1" ht="36" customHeight="1" spans="1:14">
       <c r="A14" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" t="s">
         <v>69</v>
-      </c>
-      <c r="B14" t="s">
-        <v>70</v>
       </c>
       <c r="C14">
         <v>1.1</v>
@@ -1863,7 +1860,7 @@
         <v>29</v>
       </c>
       <c r="H14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1884,10 +1881,10 @@
     </row>
     <row r="15" customFormat="1" ht="36" customHeight="1" spans="1:14">
       <c r="A15" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" t="s">
         <v>72</v>
-      </c>
-      <c r="B15" t="s">
-        <v>73</v>
       </c>
       <c r="C15">
         <v>1.1</v>
@@ -1899,7 +1896,7 @@
         <v>29</v>
       </c>
       <c r="H15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1921,45 +1918,45 @@
     <row r="16" customFormat="1" ht="54" spans="1:14">
       <c r="A16" s="7"/>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C16">
         <v>0.5</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L16" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="M16" t="s">
         <v>78</v>
       </c>
-      <c r="M16" t="s">
+      <c r="N16" s="11" t="s">
         <v>79</v>
-      </c>
-      <c r="N16" s="11" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="17" customFormat="1" ht="36" spans="1:13">
       <c r="A17" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" t="s">
         <v>81</v>
-      </c>
-      <c r="B17" t="s">
-        <v>82</v>
       </c>
       <c r="C17">
         <v>1.8</v>
@@ -1971,7 +1968,7 @@
         <v>29</v>
       </c>
       <c r="H17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1983,7 +1980,7 @@
         <v>32</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M17" t="s">
         <v>45</v>
@@ -1992,7 +1989,7 @@
     <row r="18" customFormat="1" ht="36" spans="1:13">
       <c r="A18" s="7"/>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C18">
         <v>1.1</v>
@@ -2004,16 +2001,16 @@
         <v>29</v>
       </c>
       <c r="H18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L18" s="11" t="s">
         <v>44</v>
@@ -2025,19 +2022,19 @@
     <row r="19" customFormat="1" ht="36" spans="1:13">
       <c r="A19" s="7"/>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C19">
         <v>0.5</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -2049,15 +2046,15 @@
         <v>32</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:13">
       <c r="J27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -2096,21 +2093,21 @@
         <v>29</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>90</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2123,10 +2120,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="B4" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>92</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2136,7 +2133,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="C6" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
